--- a/outputs/5. Corporate Risk Register (Final).xlsx
+++ b/outputs/5. Corporate Risk Register (Final).xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U21"/>
+  <dimension ref="A1:L21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -489,81 +489,36 @@
           <t>Risk Priority Current (low, med, high)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Schema Alignment Log</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Risk ID (Reasoning)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Description (Reasoning)</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>Project Stage (Reasoning)</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>Project Category (Reasoning)</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>Risk Owner (Reasoning)</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>Likelihood (Reasoning)</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>Impact (Reasoning)</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>Mitigating Action (Reasoning)</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Legislative changes from Central Government or EU requiring significant alteration to organisational capacity, such as impact of welfare reform and universal credit, effects of devolution, introduction of new burdens.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Monitoring Officer. Horizon scanning by Legal/CMT/Mgt Team. Service Manager responsibilities. Financial &amp; workforce planning. Membership of professional/Local Gov bodies aids horizon scanning. Mgt of change approach to mitigate significant impact to the organisation and its staff. Detailed project plans to change implementation. Respond to consultations on new legislation. Use intelligence to identify impending changes and their effects. Ensure staff trained and procedures changed. Use professional networking to identify best practice for responding to change. We respond to government consultations on changes to legislation or policy to influence its development.</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -578,91 +533,46 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Uncertainty during transition period, followed by potential legislative, funding and policy changes after UK leaves EU may adversely affect the Council and its ability to provide services.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>Environmental</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Horizon scanning by Legal Services / CMT / Heads of Service. Financial &amp; workforce planning. Membership of professional and Local Govt bodies aids horizon scanning. Management of change approach to mitigate against significant impact to the organisation and its staff. Detailed project plans to manage implementation of changes. Understanding and acting on intelligence from LGA, CIPFA and other local government sources. Identifying policies that require changing, their effects and governance as Brexit effects start.</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -680,78 +590,33 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Failure of contractors and suppliers working on the Council’s behalf to deliver services or meet agreed performance objectives, leading to additional costs or failed objectives.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Procurement</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -761,7 +626,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Procurement processes including financial checks and contract standing orders; creation of robust contracts; documented accountability and risk ownership; Service Level Agreements; contract monitoring; trained/skilled staff; project management; relationship management; Business Continuity Plans; regular monitoring of contracts and performance by Managers; ensuring contracts have risk registers and mitigation for failure.</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -776,7 +641,7 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
@@ -784,83 +649,38 @@
       <c r="L4" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Failure of IT systems leading to loss, corruption, or inaccuracy of data, resulting in service disruption, security breaches, financial penalties, and reputational damage.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>It Manager</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Implement data protection policies, information breach response plans, business continuity plans, ICT system security, and conduct regular system audits, secure off-site data backups, penetration testing, and disaster recovery testing.</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -883,73 +703,28 @@
       <c r="L5" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Insufficient staff to provide Council services and insufficient leadership and/or management capacity to deliver Council priorities. Constraints to effective workforce planning lead to poor standards of service or disruption. Service transformation and commissioning could lead to a loss of qualified staff, exposing the council to risk of service failure and legal challenge.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -959,7 +734,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Implement Learning &amp; Development framework and training. Foster a positive working environment and culture. Utilize Staff Committee and MTSP. Promote flexible working. Maintain established people policies and procedures. Implement business continuity plans and management training. Conduct 121s, Springboard staff development, and appraisals. Follow service planning process. Access interim staff via frameworks. Ensure effective sickness management and governance structures. Ensure all services have effective Workforce plans incorporated into Service Plans to prioritize work. Conduct effective succession planning. Apply project management approaches when delivering priorities and strategies.</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -977,88 +752,43 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Breach of ICT security causes loss of service. Major IT physical hardware failure or electronic attack, such as viruses, hacking or spyware, causes disruption to services and breaches of security. A further consequence could be financial penalties and reputational risk.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Cybersecurity</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Project Manager</t>
+          <t>It Manager</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Anti-virus software, Geographically distributed servers, Tested disaster recovery plan, Back-ups stored off site, Secondary power supply, Revised security policies, Critical services’ business continuity plans include manual operation. Actions Being Taken: Effective auditing of systems and data held, Data backed-up securely off-site, Regular penetration testing.</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1081,63 +811,18 @@
       <c r="L7" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>7</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Lack of access to Council premises prevents services being delivered, causing disruption of service provision.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1147,7 +832,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1157,7 +842,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Alarm and security systems; Fire drills; Business continuity plans; Emergency planning network; ICT disaster recovery and offsite testing; Relocation procedures for critical and support services; Geographically distributed sites; Remote working; Statutory building inspection and checks; Corporate Business Continuity Plans. Actions being taken: Regularly test Emergency Plan; Test service Business Continuity Plans; Ensure key emergency planning staff attend regular liaison meetings and training; Provision of 'drop down' facilities for staff.</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1175,68 +860,23 @@
         <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>8</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Funding changes make Council unsustainable. Effects: Economic changes, imposed savings requirements, changes to local government funding systems, uncertainties of pilot pension fund.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1246,7 +886,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -1256,7 +896,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Using intelligence to model and plan for future changes and risks and move away from reliance on Govt funding to balance our budget. Regular monitoring of current position and reporting to Members. Workforce planning covers all scenarios. Inclusion in national working groups, modelling and lobbying for funding system after RSG ceases. Sharing Council’s Efficiency Plan with the Government allows guaranteed multi-year grant settlement raising funding certainty. Shared services and partnership working.</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1274,78 +914,33 @@
         <v>3</v>
       </c>
       <c r="K9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>9</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>The Council’s ability to cope with a natural disaster. Natural disaster; malicious or accidental incident affects support required by civilians or disrupts existing Council services.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1355,7 +950,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Emergency plan; Emergency planning exercises beyond the district; Business continuity plans; Regular exercise and joint public sector workshops for Emergency Planning; Emergency Planning Communications Strategy; Review of approach with partner organisations as a result of lessons learned from ‘near miss’ flood events; Local Resilience Forum; Regularly test Emergency Plan; Test Service Business Continuity Plans; Ensure key emergency planning staff attend regular liaison meetings and training.</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -1370,71 +965,26 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K10" t="n">
         <v>4</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Med</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
+          <t>High</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>10</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Major health and safety incident at Council leads to costs for inquiry, disruption to service and possible prosecution</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1444,7 +994,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1454,7 +1004,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Health &amp; Safety Panel; H&amp;S procedures addressed at every service area; H&amp;S audits in all services; Specialist H&amp;S advisor; Corporate wide H&amp;S training; Insurance; Aligned Port Health and Safety arrangements; Port Management Group and annual independent audit; Robust sickness management processes; Ensure health and safety is standard agenda on all team meetings; Ensure equipment inventory and inspections are up to date; Review Risk Assessments and Action Plans; Capture Port near misses and assess learning points</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -1469,71 +1019,26 @@
         </is>
       </c>
       <c r="J11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>11</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Potential for fraud, corruption, malpractice or error, by internal or external threats. In additional to immediate financial loss, this could harm reputation and lead to additional inquiry costs and penalties.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1543,7 +1048,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1553,7 +1058,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Anti-fraud &amp; corruption policy/ strategy, Financial Regulations / Standing Ord, Codes of conduct, Appropriately trained staff, Appropriate culture and risk awareness, Segregation of duties, Supported financial mgt system, Budget monitoring regime, Internal Audit review of sys /and controls, Bribery &amp; corruption / fraud risk assessments, Indemnity insurance, Whistle-blowing procedure, Annual Governance Statement, ARP fraud resource, National Fraud Initiative, Increase staff vigilance, Fraud awareness training for Managers, Raise profile internally and externally for successful prosecutions</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1568,71 +1073,26 @@
         </is>
       </c>
       <c r="J12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>12</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Failure of external investment institutions affecting availability of funds or return on investment, reducing cash flow and resource availability.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1642,7 +1102,7 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1652,7 +1112,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Policy for maximum investment/borrowing levels limits liability. Credit ratings. Financial management. Reserves. Insurance. Medium Term Financial Strategy. Treasury Management Strategy. Effective Treasury Management strategy. Robust auditing of processes and policies.</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -1667,81 +1127,36 @@
         </is>
       </c>
       <c r="J13" t="n">
+        <v>4</v>
+      </c>
+      <c r="K13" t="n">
         <v>2</v>
       </c>
-      <c r="K13" t="n">
-        <v>4</v>
-      </c>
       <c r="L13" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>13</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Failure of Governance in major partners or in the Council as a result of partnership working. Partnership governance not adopted or followed, leading to unachieved priorities and poor performance by major partner agencies: Cambs and Peterborough Combined Authority, Anglia Revenues Partnership, CNC Building Control, Shared Planning, Payroll delivered by Bedford BC.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -1751,7 +1166,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>FSP, Fenland Public Service Board, Cabinet and O&amp;S, bi-annual stakeholder events ensure accountability. ARP Joint Committee and Operational Improvement Board, Cabinet, O&amp;S, joint risk registers. CNC Joint Members Board, Cabinet plus O&amp;S. Shared Planning Board, Cabinet plus Overview and Scrutiny, joint performance indicators. Project plans / performance monitoring shared risk registers. PCCA Membership. Assurance that governance models correctly followed and in the Council’s interests. Support Members in governance of partnership bodies. Internal Audit partnership arrangements. Ensure that the Council’s interests are protected as Members of the Combined Authority and as Officers working on joint projects. Ensure all Partners have robust Business Continuity Plans in place. GDPR compliance. Robust ICT governance processes.</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -1774,73 +1189,28 @@
       <c r="L14" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>14</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Failure to achieve required savings targets, resulting in greater than budgeted costs and potential risk of Council not being able to set a balanced budget.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1850,7 +1220,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Heightened analysis of budgets and services; Implement Service Transformation; Implement Procurement Strategy; Corporate plan; Pursue action to increase income streams; Performance Management Framework; Budget and performance monitoring; Robust Workforce planning; Project Management processes.</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -1873,73 +1243,28 @@
       <c r="L15" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>15</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Over-run of major Council projects in time or cost. Failure to manage projects effectively leads to overruns on time or cost and failure to achieve project aims, resulting in reputational damage.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Programme</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1949,7 +1274,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Robust project management. Effective risk registers for projects. Project Management methodology. Contract Standing Orders &amp; Financial Regulations. Service plans. Budgetary control. Management and Portfolio Holder oversight.</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -1964,7 +1289,7 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K16" t="n">
         <v>3</v>
@@ -1972,73 +1297,28 @@
       <c r="L16" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>16</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Service provision and performance affected by organisational change, industrial action and/or staff sickness resulting in complaints, poor performance and possible further costs.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Operations</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -2048,7 +1328,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Business continuity plans for each service. Workforce planning, which includes succession planning for key roles and talent management. A comprehensive programme of health surveillance for certain employee groups. Trained Mental Health First Aiders, stress awareness training, and resilience training in place. Staff engagement and consultation processes. Robust sickness absence management and regular performance monitoring.</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -2063,7 +1343,7 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
         <v>3</v>
@@ -2071,63 +1351,18 @@
       <c r="L17" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>17</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Political changes in national priorities may result in immediate changes that require additional resource to achieve and fail to reflect priorities determined by consultation.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -2137,7 +1372,7 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Legislation</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -2147,7 +1382,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Financial &amp; workforce planning; Monitoring by CMT and resultant Cabinet reports; Clear corporate planning and regular performance monitoring; Effective service &amp; financial planning; Respond to national consultation on key policy changes; Membership of LGA as a Council Outside Body; Understanding and acting on intelligence from LGA, CIPFA and other local government sources; Resources identified, approved and implemented without delay; Constant monitoring; Horizon scanning via professional bodies; Joint/collaborative working.</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -2162,81 +1397,36 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>18</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Capital funding strategy failure. Financial risks of capital funding shortfalls leading to increased burden to the Council. Potential for marginal deficit in capital program if future funding is not realised.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -2246,7 +1436,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Asset management plan. Asset disposal linked to capital programme. Corporate Asset Team. CMT monitoring of capital receipts/effect on capital programme. Regular Cabinet review of the capital programme, member with responsibility for assets. Additional funding opportunities identified and pursued where possible. Project lead monitors site valuations linked to economic development proposals. Marketing and identification of potential land purchasers, flexibility of planning guidance aligned to market needs. Continued consultation with economic partners. Forward planning and horizon scanning. Regular high level monitoring of direction of travel and mitigation required. Asset Management Plan. Asset disposal strategy.</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -2261,71 +1451,26 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>19</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Poor communications with stakeholders and staff leads to poorly informed direction of resources and lack of support for change</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -2335,7 +1480,7 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Services</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -2345,7 +1490,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Internal and external regular publications, staff and management meetings, regular staff communication from the Chief Executive, key stakeholder networks for consultation, forums for perceived hard to reach groups, co-ordinated press releases, Comments, Compliments and Complaints monitoring and reporting procedure, Customer Service Excellence accreditation, consultation strategy, Management, Trade Union and Staff Partnership group (MTSP). Actions being taken: CSE Action Plan, staff survey, public consultations on key issues, 3cs refresher training, team meetings, “What’s Breaking” communication and “Horse’s Mouth” updates from the Chief Executive to all staff.</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -2368,73 +1513,28 @@
       <c r="L20" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>R-UNK</t>
+          <t>20</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Unspecified</t>
+          <t>Commercial uncertainties associated with decisions taken as part of the Council’s Commercial and Investment Strategy.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Operation</t>
+          <t>Pre Construction</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Materials</t>
+          <t>Financial</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -2444,7 +1544,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Monitor and evaluate.</t>
+          <t>Robust oversight and governance arrangements, expert professional advice, robust budget management, thorough project management and business cases process.</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -2459,59 +1559,14 @@
         </is>
       </c>
       <c r="J21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
           <t>Med</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Tidak ada alasan.</t>
         </is>
       </c>
     </row>
